--- a/resources/templates/standard/J3100-03.xlsx
+++ b/resources/templates/standard/J3100-03.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>4M 변경 관리대장</t>
   </si>
@@ -777,10 +780,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -802,18 +807,18 @@
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC1" s="4"/>
     </row>
@@ -850,7 +855,7 @@
     </row>
     <row r="3" ht="50.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -863,108 +868,108 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M3" s="8"/>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
       <c r="P3" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
       <c r="T3" s="9"/>
       <c r="U3" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V3" s="10"/>
       <c r="W3" s="10"/>
       <c r="X3" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y3" s="11"/>
       <c r="Z3" s="11"/>
       <c r="AA3" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB3" s="13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC3" s="13"/>
     </row>
     <row r="4" ht="50.25" customHeight="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R4" s="19"/>
       <c r="S4" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T4" s="19"/>
       <c r="U4" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V4" s="20"/>
       <c r="W4" s="21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X4" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y4" s="21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z4" s="21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA4" s="12"/>
       <c r="AB4" s="13"/>
@@ -987,25 +992,25 @@
       <c r="N5" s="18"/>
       <c r="O5" s="17"/>
       <c r="P5" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="S5" s="9" t="s">
-        <v>36</v>
-      </c>
       <c r="T5" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U5" s="22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V5" s="22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W5" s="21"/>
       <c r="X5" s="21"/>
